--- a/Ranking-python-by-rmp/config_overrides.xlsx
+++ b/Ranking-python-by-rmp/config_overrides.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18750" windowHeight="5600"/>
+    <workbookView windowWidth="18750" windowHeight="6200"/>
   </bookViews>
   <sheets>
     <sheet name="config_overrides" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>variable_name</t>
   </si>
@@ -52,6 +52,12 @@
   <si>
     <t>fresh_feed_quantity</t>
   </si>
+  <si>
+    <t>NUM_FURNACES</t>
+  </si>
+  <si>
+    <t>NUM_PASSES</t>
+  </si>
 </sst>
 </file>
 
@@ -63,7 +69,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,13 +89,6 @@
       <color rgb="FFCE9178"/>
       <name val="Consolas"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -566,148 +565,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1132,12 +1131,20 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3">
+        <v>9</v>
+      </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3">
+        <v>8</v>
+      </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3"/>
